--- a/готовое_решение/тест/03_нули_в_приоритетах/выход/результат_распределения.xlsx
+++ b/готовое_решение/тест/03_нули_в_приоритетах/выход/результат_распределения.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Результат" sheetId="1" r:id="rId1"/>
+    <sheet name="Количество_по_трекам" sheetId="2" r:id="rId2"/>
+    <sheet name="Без_выбора" sheetId="3" r:id="rId3"/>
+    <sheet name="Приоритеты_1_2" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -68,6 +71,21 @@
           <t>рейтинг</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>выбор трека</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>статус без выбора</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>приоритеты</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -86,6 +104,21 @@
       <c r="D2">
         <v>103.602554</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>сделает выбор позднее</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Трек А: 0, Трек В: 0, Трек С: 0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -104,6 +137,21 @@
       <c r="D3">
         <v>96.935724</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>статус не указан</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Трек А: 0, Трек В: 0, Трек С: 0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -122,6 +170,21 @@
       <c r="D4">
         <v>90.268882</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>статус не указан</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Трек А: 0, Трек В: 0, Трек С: 0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -140,6 +203,21 @@
       <c r="D5">
         <v>83.602046</v>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>статус не указан</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Трек А: 0, Трек В: 0, Трек С: 0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -158,6 +236,21 @@
       <c r="D6">
         <v>70.268376</v>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>статус не указан</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Трек А: 0, Трек В: 0, Трек С: 0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -175,6 +268,324 @@
       </c>
       <c r="D7">
         <v>63.60154</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>уйдет</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Трек А: 0, Трек В: 0, Трек С: 0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>трек</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>назначено студентов</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>приоритет 1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>приоритет 1 или 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Трек А</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Трек В</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Трек С</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id ученика</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>трек</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>место в рейтинге</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>рейтинг</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>статус без выбора</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Трек А</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>103.602554</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>сделает выбор позднее</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Трек В</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>96.935724</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>статус не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Трек С</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>90.268882</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>статус не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Трек А</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>83.602046</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>статус не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3106</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Трек В</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>70.268376</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>статус не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Трек С</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>63.60154</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>уйдет</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>трек</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>количество студентов с приоритетом 1 или 2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>id студентов с приоритетом 1 или 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Трек А</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Трек В</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Трек С</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/готовое_решение/тест/03_нули_в_приоритетах/выход/результат_распределения.xlsx
+++ b/готовое_решение/тест/03_нули_в_приоритетах/выход/результат_распределения.xlsx
@@ -3,9 +3,10 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Результат" sheetId="1" r:id="rId1"/>
-    <sheet name="Количество_по_трекам" sheetId="2" r:id="rId2"/>
-    <sheet name="Без_выбора" sheetId="3" r:id="rId3"/>
-    <sheet name="Приоритеты_1_2" sheetId="4" r:id="rId4"/>
+    <sheet name="Гипотеза" sheetId="2" r:id="rId2"/>
+    <sheet name="Количество_по_трекам" sheetId="3" r:id="rId3"/>
+    <sheet name="Без_выбора" sheetId="4" r:id="rId4"/>
+    <sheet name="Приоритеты_1_2" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -73,15 +74,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>режим распределения</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>попадание по предпочтению</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>выбор трека</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>статус без выбора</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>приоритеты</t>
         </is>
@@ -106,15 +117,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>выбор не указан</t>
+          <t>с рейтингом</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>сделает выбор позднее</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Трек А: 0, Трек В: 0, Трек С: 0</t>
         </is>
@@ -139,15 +160,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>выбор не указан</t>
+          <t>с рейтингом</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>статус не указан</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Трек А: 0, Трек В: 0, Трек С: 0</t>
         </is>
@@ -172,15 +203,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>выбор не указан</t>
+          <t>с рейтингом</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>статус не указан</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Трек А: 0, Трек В: 0, Трек С: 0</t>
         </is>
@@ -205,15 +246,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>выбор не указан</t>
+          <t>с рейтингом</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>статус не указан</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Трек А: 0, Трек В: 0, Трек С: 0</t>
         </is>
@@ -238,15 +289,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>выбор не указан</t>
+          <t>с рейтингом</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>статус не указан</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Трек А: 0, Трек В: 0, Трек С: 0</t>
         </is>
@@ -271,15 +332,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>выбор не указан</t>
+          <t>с рейтингом</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>выбор не указан</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>уйдет</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Трек А: 0, Трек В: 0, Трек С: 0</t>
         </is>
@@ -295,71 +366,129 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>трек</t>
+          <t>параметр</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>назначено студентов</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>приоритет 1</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>приоритет 1 или 2</t>
+          <t>значение</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Трек А</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
+          <t>режим распределения</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>с учетом рейтинга</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Трек В</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
+          <t>оценки участвуют в распределении</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Трек С</t>
+          <t>всего студентов</t>
         </is>
       </c>
       <c r="B4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>студентов с указанными предпочтениями</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>студентов без выбора</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>назначено на приоритет 1</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>назначено на приоритет 2</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>назначено вне приоритетов или без выбора</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>минимум по треку</t>
+        </is>
+      </c>
+      <c r="B10">
         <v>2</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>максимум по треку</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>гипотеза</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>используется режим с рейтингом</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -372,166 +501,71 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id ученика</t>
+          <t>трек</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>трек</t>
+          <t>назначено студентов</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>место в рейтинге</t>
+          <t>приоритет 1</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>рейтинг</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>статус без выбора</t>
+          <t>приоритет 1 или 2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3102</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>Трек А</t>
         </is>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>103.602554</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>сделает выбор позднее</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3105</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>Трек В</t>
         </is>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>96.935724</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>статус не указан</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3104</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>Трек С</t>
         </is>
       </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
       <c r="C4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>90.268882</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>статус не указан</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3101</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Трек А</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>83.602046</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>статус не указан</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3106</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Трек В</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>70.268376</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>статус не указан</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Трек С</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>63.60154</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>уйдет</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -544,6 +578,178 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>id ученика</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>трек</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>место в рейтинге</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>рейтинг</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>статус без выбора</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Трек А</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>103.602554</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>сделает выбор позднее</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Трек В</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>96.935724</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>статус не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Трек С</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>90.268882</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>статус не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Трек А</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>83.602046</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>статус не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3106</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Трек В</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>70.268376</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>статус не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Трек С</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>63.60154</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>уйдет</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>трек</t>
         </is>
       </c>
